--- a/backend/wp_templates/H/H3 投资性房地产.xlsx
+++ b/backend/wp_templates/H/H3 投资性房地产.xlsx
@@ -26279,58 +26279,6 @@
   </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-  <oleObjects>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject shapeId="6145" progId="Equation.3" r:id="rId3">
-          <objectPr defaultSize="0" r:id="rId4">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>106680</xdr:colOff>
-                <xdr:row>50</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>52</xdr:row>
-                <xdr:rowOff>137160</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject shapeId="6145" progId="Equation.3" r:id="rId3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject shapeId="6146" progId="Equation.3" r:id="rId5">
-          <objectPr defaultSize="0" r:id="rId6">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>655320</xdr:colOff>
-                <xdr:row>50</xdr:row>
-                <xdr:rowOff>144780</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>198120</xdr:colOff>
-                <xdr:row>52</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject shapeId="6146" progId="Equation.3" r:id="rId5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </oleObjects>
 </worksheet>
 </file>
 

--- a/backend/wp_templates/H/H3 投资性房地产.xlsx
+++ b/backend/wp_templates/H/H3 投资性房地产.xlsx
@@ -37904,7 +37904,9 @@
       </c>
       <c r="P13" s="386"/>
       <c r="Q13" s="382"/>
-      <c r="R13" s="387"/>
+      <c r="R13" s="387">
+        <f>P13+Q13</f>
+      </c>
       <c r="S13" s="385"/>
       <c r="T13" s="385"/>
       <c r="U13" s="276">
@@ -37963,7 +37965,9 @@
       </c>
       <c r="P14" s="386"/>
       <c r="Q14" s="382"/>
-      <c r="R14" s="387"/>
+      <c r="R14" s="387">
+        <f>P14+Q14</f>
+      </c>
       <c r="S14" s="385"/>
       <c r="T14" s="385"/>
       <c r="U14" s="276">
@@ -38022,7 +38026,9 @@
       </c>
       <c r="P15" s="386"/>
       <c r="Q15" s="382"/>
-      <c r="R15" s="387"/>
+      <c r="R15" s="387">
+        <f>P15+Q15</f>
+      </c>
       <c r="S15" s="385"/>
       <c r="T15" s="385"/>
       <c r="U15" s="276">
@@ -38081,7 +38087,9 @@
       </c>
       <c r="P16" s="386"/>
       <c r="Q16" s="382"/>
-      <c r="R16" s="387"/>
+      <c r="R16" s="387">
+        <f>P16+Q16</f>
+      </c>
       <c r="S16" s="385"/>
       <c r="T16" s="385"/>
       <c r="U16" s="276">
@@ -38140,7 +38148,9 @@
       </c>
       <c r="P17" s="386"/>
       <c r="Q17" s="382"/>
-      <c r="R17" s="387"/>
+      <c r="R17" s="387">
+        <f>P17+Q17</f>
+      </c>
       <c r="S17" s="385"/>
       <c r="T17" s="385"/>
       <c r="U17" s="276">
@@ -38199,7 +38209,9 @@
       </c>
       <c r="P18" s="386"/>
       <c r="Q18" s="382"/>
-      <c r="R18" s="387"/>
+      <c r="R18" s="387">
+        <f>P18+Q18</f>
+      </c>
       <c r="S18" s="385"/>
       <c r="T18" s="385"/>
       <c r="U18" s="276">
@@ -38258,7 +38270,9 @@
       </c>
       <c r="P19" s="391"/>
       <c r="Q19" s="389"/>
-      <c r="R19" s="387"/>
+      <c r="R19" s="387">
+        <f>P19+Q19</f>
+      </c>
       <c r="S19" s="385"/>
       <c r="T19" s="385"/>
       <c r="U19" s="276">
@@ -38317,7 +38331,9 @@
       </c>
       <c r="P20" s="391"/>
       <c r="Q20" s="389"/>
-      <c r="R20" s="387"/>
+      <c r="R20" s="387">
+        <f>P20+Q20</f>
+      </c>
       <c r="S20" s="385"/>
       <c r="T20" s="385"/>
       <c r="U20" s="276">
@@ -38376,7 +38392,9 @@
       </c>
       <c r="P21" s="391"/>
       <c r="Q21" s="389"/>
-      <c r="R21" s="387"/>
+      <c r="R21" s="387">
+        <f>P21+Q21</f>
+      </c>
       <c r="S21" s="385"/>
       <c r="T21" s="385"/>
       <c r="U21" s="276">
@@ -38435,7 +38453,9 @@
       </c>
       <c r="P22" s="391"/>
       <c r="Q22" s="389"/>
-      <c r="R22" s="387"/>
+      <c r="R22" s="387">
+        <f>P22+Q22</f>
+      </c>
       <c r="S22" s="385"/>
       <c r="T22" s="385"/>
       <c r="U22" s="276">
@@ -38494,7 +38514,9 @@
       </c>
       <c r="P23" s="391"/>
       <c r="Q23" s="389"/>
-      <c r="R23" s="387"/>
+      <c r="R23" s="387">
+        <f>P23+Q23</f>
+      </c>
       <c r="S23" s="385"/>
       <c r="T23" s="385"/>
       <c r="U23" s="276">
@@ -38553,7 +38575,9 @@
       </c>
       <c r="P24" s="391"/>
       <c r="Q24" s="389"/>
-      <c r="R24" s="387"/>
+      <c r="R24" s="387">
+        <f>P24+Q24</f>
+      </c>
       <c r="S24" s="385"/>
       <c r="T24" s="385"/>
       <c r="U24" s="276">
@@ -38612,7 +38636,9 @@
       </c>
       <c r="P25" s="391"/>
       <c r="Q25" s="389"/>
-      <c r="R25" s="387"/>
+      <c r="R25" s="387">
+        <f>P25+Q25</f>
+      </c>
       <c r="S25" s="385"/>
       <c r="T25" s="385"/>
       <c r="U25" s="276">
@@ -38671,7 +38697,9 @@
       </c>
       <c r="P26" s="391"/>
       <c r="Q26" s="389"/>
-      <c r="R26" s="387"/>
+      <c r="R26" s="387">
+        <f>P26+Q26</f>
+      </c>
       <c r="S26" s="385"/>
       <c r="T26" s="385"/>
       <c r="U26" s="276">
